--- a/sources/2B_Manha_2_Bimestre.xlsx
+++ b/sources/2B_Manha_2_Bimestre.xlsx
@@ -178,6 +178,27 @@
     <x:t>94%</x:t>
   </x:si>
   <x:si>
+    <x:t>ADRIELLE JESUS VELOZO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKAYOARA DAFNY CASSIANO ANASTACIO DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -187,18 +208,12 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
@@ -229,18 +244,12 @@
     <x:t>ANA CLARA APARECIDA DE JESUS</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
     <x:t>97%</x:t>
   </x:si>
   <x:si>
     <x:t>ANDREW GABRIEL SANTOS CESTREM</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
     <x:t>93%</x:t>
   </x:si>
   <x:si>
@@ -286,223 +295,220 @@
     <x:t>Não Comparecimento</x:t>
   </x:si>
   <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL HENRIQUE MIGUEL DEVAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL MARQUES DANTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEOVANNA FEITOSA NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIOVANNA ARIADNY BARBOSA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIULIA VOIGT TAVARES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME DA SILVA AMADO RAYMUNDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME HENRIQUE OLIVEIRA AGUIAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME RIBEIRO DE LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO LIMA MACIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HELENA MAURICIO PEDRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HELOAH REBECA MONTEIRO DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HIRIS CRYSTIARA DUTRA CLEMENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUGO DA SILVA OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZAQUE GONZAGA HERNANDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOÃO VICTOR MACEDO DOS REIS BENEDICTO</x:t>
+  </x:si>
+  <x:si>
     <x:t>67%</x:t>
   </x:si>
   <x:si>
-    <x:t>GABRIEL HENRIQUE MIGUEL DEVAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL MARQUES DANTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEOVANNA FEITOSA NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIOVANNA ARIADNY BARBOSA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIULIA VOIGT TAVARES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME DA SILVA AMADO RAYMUNDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME RIBEIRO DE LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO LIMA MACIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HELENA MAURICIO PEDRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74%</x:t>
+    <x:t>JULIA ALMEIDA GUIMARAES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JÚLIA SILVA SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JULIO CESAR MARTINS VIEIRA DE CARVALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYQUE FREIRES DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KEIRRISON DOS SANTOS FARIAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KEMILLY GOES DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KYARA GONCALVES RODRIGUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEANDRO DE MAGALHAES SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LORENNA BARAUNA VENANCIO DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS MASSI AGUENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIS FELIPE CARDOSO DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZA ALVES SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCELO APARECIDO GOMES JUNIOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS HENRIQUE DE OLIVEIRA CASTILHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEL GLÉCIO DIAS SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLAS GOMES DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLE DE BRITO OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLE MALTA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTAVIO SILVA SALDANHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO AUGUSTO ROMÃO SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL SOUZA REIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAELLA SILVA PINHEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REBECA ISAQUE DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICHARD OLIVEIRA BANULS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALLACE CUNHA PIRES ALVES</x:t>
   </x:si>
   <x:si>
     <x:t>69%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HELOAH REBECA MONTEIRO DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HIRIS CRYSTIARA DUTRA CLEMENTINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUGO DA SILVA OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZAQUE GONZAGA HERNANDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JULIA ALMEIDA GUIMARAES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JÚLIA SILVA SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JULIO CESAR MARTINS VIEIRA DE CARVALHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYQUE FREIRES DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KEIRRISON DOS SANTOS FARIAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KEMILLY GOES DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KYARA GONCALVES RODRIGUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LORENNA BARAUNA VENANCIO DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS MASSI AGUENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUIS FELIPE CARDOSO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUIZA ALVES SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARCELO APARECIDO GOMES JUNIOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS HENRIQUE DE OLIVEIRA CASTILHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEL GLÉCIO DIAS SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLAS GOMES DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLE DE BRITO OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLE MALTA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTAVIO SILVA SALDANHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO AUGUSTO ROMÃO SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAEL SOUZA REIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAELLA SILVA PINHEIRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REBECA ISAQUE DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICHARD OLIVEIRA BANULS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALLACE CUNHA PIRES ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADRIELLE JESUS VELOZO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME HENRIQUE OLIVEIRA AGUIAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOÃO VICTOR MACEDO DOS REIS BENEDICTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEANDRO DE MAGALHAES SOUZA</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -1561,10 +1567,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AW13" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX13" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY13" s="12">
         <x:v>0</x:v>
@@ -1584,16 +1590,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F14" s="12" t="s">
         <x:v>47</x:v>
@@ -1614,10 +1620,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M14" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N14" s="12" t="s">
         <x:v>47</x:v>
@@ -1626,10 +1632,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P14" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R14" s="12" t="s">
         <x:v>47</x:v>
@@ -1638,7 +1644,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T14" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
         <x:v>52</x:v>
@@ -1662,10 +1668,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AB14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
         <x:v>47</x:v>
@@ -1674,10 +1680,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AF14" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AG14" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="AG14" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>47</x:v>
@@ -1686,10 +1692,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AK14" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="AK14" s="12" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
         <x:v>47</x:v>
@@ -1710,10 +1716,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AS14" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="AS14" s="12" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
         <x:v>47</x:v>
@@ -1722,42 +1728,42 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY14" s="12">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AZ14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA14" s="12">
-        <x:v>166</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BB14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:54">
       <x:c r="A15" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
         <x:v>47</x:v>
@@ -1778,10 +1784,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N15" s="12" t="s">
         <x:v>47</x:v>
@@ -1790,10 +1796,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P15" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R15" s="12" t="s">
         <x:v>47</x:v>
@@ -1802,10 +1808,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T15" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
         <x:v>47</x:v>
@@ -1826,10 +1832,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
         <x:v>47</x:v>
@@ -1838,10 +1844,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AF15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
         <x:v>47</x:v>
@@ -1850,13 +1856,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AJ15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM15" s="12">
         <x:v>3</x:v>
@@ -1874,10 +1880,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
         <x:v>47</x:v>
@@ -1886,22 +1892,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AX15" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY15" s="12">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AZ15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BA15" s="12">
-        <x:v>59</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>65</x:v>
@@ -1912,13 +1918,13 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
         <x:v>47</x:v>
@@ -1942,10 +1948,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N16" s="12" t="s">
         <x:v>47</x:v>
@@ -1954,10 +1960,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R16" s="12" t="s">
         <x:v>47</x:v>
@@ -1966,10 +1972,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
         <x:v>47</x:v>
@@ -1990,10 +1996,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
         <x:v>47</x:v>
@@ -2002,10 +2008,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF16" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
         <x:v>47</x:v>
@@ -2017,10 +2023,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AM16" s="12">
         <x:v>4</x:v>
@@ -2038,10 +2044,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT16" s="12" t="s">
         <x:v>47</x:v>
@@ -2050,42 +2056,42 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AV16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW16" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX16" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY16" s="12">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="AZ16" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BA16" s="12">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB16" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:54">
       <x:c r="A17" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
         <x:v>47</x:v>
@@ -2106,10 +2112,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
         <x:v>47</x:v>
@@ -2118,7 +2124,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P17" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
         <x:v>47</x:v>
@@ -2133,7 +2139,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
         <x:v>47</x:v>
@@ -2154,10 +2160,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AB17" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="s">
         <x:v>47</x:v>
@@ -2166,10 +2172,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF17" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH17" s="12" t="s">
         <x:v>47</x:v>
@@ -2178,13 +2184,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AJ17" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AM17" s="12">
         <x:v>5</x:v>
@@ -2202,7 +2208,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AR17" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
         <x:v>47</x:v>
@@ -2214,42 +2220,42 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY17" s="12">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AZ17" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BA17" s="12">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BB17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:54">
       <x:c r="A18" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
         <x:v>47</x:v>
@@ -2270,10 +2276,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>47</x:v>
@@ -2282,7 +2288,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
         <x:v>47</x:v>
@@ -2294,10 +2300,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
         <x:v>47</x:v>
@@ -2318,7 +2324,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
         <x:v>47</x:v>
@@ -2330,10 +2336,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>47</x:v>
@@ -2342,10 +2348,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>47</x:v>
@@ -2366,7 +2372,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
         <x:v>47</x:v>
@@ -2378,39 +2384,39 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AV18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY18" s="12">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AZ18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA18" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="BB18" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:54">
       <x:c r="A19" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
         <x:v>47</x:v>
@@ -2434,7 +2440,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="L19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M19" s="12" t="s">
         <x:v>47</x:v>
@@ -2446,7 +2452,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="s">
         <x:v>47</x:v>
@@ -2458,7 +2464,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
         <x:v>47</x:v>
@@ -2482,10 +2488,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="s">
         <x:v>47</x:v>
@@ -2494,10 +2500,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
         <x:v>47</x:v>
@@ -2506,13 +2512,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM19" s="12">
         <x:v>7</x:v>
@@ -2530,7 +2536,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
         <x:v>47</x:v>
@@ -2542,39 +2548,39 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY19" s="12">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ19" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA19" s="12">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:54">
       <x:c r="A20" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
         <x:v>47</x:v>
@@ -2598,10 +2604,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>47</x:v>
@@ -2610,10 +2616,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>47</x:v>
@@ -2622,10 +2628,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
         <x:v>47</x:v>
@@ -2646,10 +2652,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>47</x:v>
@@ -2658,10 +2664,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
         <x:v>47</x:v>
@@ -2670,13 +2676,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AK20" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="AK20" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="AL20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AM20" s="12">
         <x:v>8</x:v>
@@ -2694,10 +2700,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
         <x:v>47</x:v>
@@ -2706,39 +2712,39 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY20" s="12">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AZ20" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="BA20" s="12">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="AZ20" s="12" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="BA20" s="12">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="BB20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:54">
       <x:c r="A21" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
         <x:v>47</x:v>
@@ -2762,10 +2768,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>47</x:v>
@@ -2774,10 +2780,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
         <x:v>47</x:v>
@@ -2786,10 +2792,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
         <x:v>47</x:v>
@@ -2810,7 +2816,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
         <x:v>47</x:v>
@@ -2822,10 +2828,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>47</x:v>
@@ -2834,10 +2840,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>47</x:v>
@@ -2858,10 +2864,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
         <x:v>47</x:v>
@@ -2870,25 +2876,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AV21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY21" s="12">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AZ21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA21" s="12">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:54">
@@ -2896,16 +2902,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
         <x:v>47</x:v>
@@ -2926,10 +2932,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N22" s="12" t="s">
         <x:v>47</x:v>
@@ -2938,10 +2944,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="P22" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R22" s="12" t="s">
         <x:v>47</x:v>
@@ -2950,10 +2956,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
         <x:v>47</x:v>
@@ -2974,10 +2980,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>47</x:v>
@@ -2986,10 +2992,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
         <x:v>47</x:v>
@@ -2998,13 +3004,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM22" s="12">
         <x:v>10</x:v>
@@ -3022,10 +3028,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
         <x:v>47</x:v>
@@ -3034,22 +3040,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX22" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY22" s="12">
-        <x:v>73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ22" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA22" s="12">
-        <x:v>112</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BB22" s="12" t="s">
         <x:v>82</x:v>
@@ -3060,16 +3066,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
         <x:v>47</x:v>
@@ -3090,10 +3096,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>47</x:v>
@@ -3102,10 +3108,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
         <x:v>47</x:v>
@@ -3114,10 +3120,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
         <x:v>47</x:v>
@@ -3138,10 +3144,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
         <x:v>47</x:v>
@@ -3150,10 +3156,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
         <x:v>47</x:v>
@@ -3162,13 +3168,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AM23" s="12">
         <x:v>11</x:v>
@@ -3186,10 +3192,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
         <x:v>47</x:v>
@@ -3198,42 +3204,42 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY23" s="12">
-        <x:v>21</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="BA23" s="12">
-        <x:v>26</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:54">
       <x:c r="A24" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>47</x:v>
@@ -3254,10 +3260,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>47</x:v>
@@ -3266,10 +3272,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
         <x:v>47</x:v>
@@ -3278,10 +3284,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
         <x:v>47</x:v>
@@ -3302,10 +3308,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>47</x:v>
@@ -3314,10 +3320,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>47</x:v>
@@ -3326,13 +3332,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AM24" s="12">
         <x:v>12</x:v>
@@ -3350,10 +3356,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
         <x:v>47</x:v>
@@ -3362,25 +3368,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AV24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY24" s="12">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AZ24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA24" s="12">
-        <x:v>146</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:54">
@@ -3388,7 +3394,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="12">
         <x:v>13</x:v>
@@ -3529,10 +3535,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AW25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY25" s="12">
         <x:v>0</x:v>
@@ -3541,18 +3547,18 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA25" s="12">
-        <x:v>24</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="BB25" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:54">
       <x:c r="A26" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="12">
         <x:v>14</x:v>
@@ -3693,10 +3699,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY26" s="12">
         <x:v>0</x:v>
@@ -3705,24 +3711,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA26" s="12">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BB26" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:54">
       <x:c r="A27" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
         <x:v>47</x:v>
@@ -3746,7 +3752,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
         <x:v>47</x:v>
@@ -3758,10 +3764,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
         <x:v>47</x:v>
@@ -3770,10 +3776,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
         <x:v>47</x:v>
@@ -3794,7 +3800,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
         <x:v>47</x:v>
@@ -3806,10 +3812,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>47</x:v>
@@ -3818,13 +3824,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM27" s="12">
         <x:v>15</x:v>
@@ -3842,7 +3848,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
         <x:v>47</x:v>
@@ -3854,7 +3860,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
         <x:v>47</x:v>
@@ -3863,30 +3869,30 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY27" s="12">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA27" s="12">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:54">
       <x:c r="A28" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
         <x:v>47</x:v>
@@ -3910,10 +3916,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>47</x:v>
@@ -3922,10 +3928,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
         <x:v>47</x:v>
@@ -3934,10 +3940,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
         <x:v>47</x:v>
@@ -3958,10 +3964,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>47</x:v>
@@ -3970,10 +3976,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>47</x:v>
@@ -3982,13 +3988,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AM28" s="12">
         <x:v>16</x:v>
@@ -4006,10 +4012,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
         <x:v>47</x:v>
@@ -4018,25 +4024,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX28" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY28" s="12">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BA28" s="12">
-        <x:v>90</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:54">
@@ -4044,16 +4050,16 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>47</x:v>
@@ -4074,10 +4080,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
         <x:v>47</x:v>
@@ -4086,10 +4092,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>47</x:v>
@@ -4098,10 +4104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>47</x:v>
@@ -4122,10 +4128,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>47</x:v>
@@ -4134,10 +4140,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>47</x:v>
@@ -4146,13 +4152,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM29" s="12">
         <x:v>17</x:v>
@@ -4170,10 +4176,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
         <x:v>47</x:v>
@@ -4182,42 +4188,42 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY29" s="12">
-        <x:v>92</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BA29" s="12">
-        <x:v>159</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:54">
       <x:c r="A30" s="11" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>47</x:v>
@@ -4238,10 +4244,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>47</x:v>
@@ -4250,10 +4256,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>47</x:v>
@@ -4262,10 +4268,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
         <x:v>47</x:v>
@@ -4286,10 +4292,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AC30" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="AC30" s="12" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>47</x:v>
@@ -4298,10 +4304,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>47</x:v>
@@ -4310,13 +4316,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AM30" s="12">
         <x:v>18</x:v>
@@ -4334,10 +4340,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
         <x:v>47</x:v>
@@ -4346,25 +4352,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY30" s="12">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BA30" s="12">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="BB30" s="12" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="BA30" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="BB30" s="12" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:54">
@@ -4372,16 +4378,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>47</x:v>
@@ -4402,10 +4408,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M31" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="M31" s="12" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>47</x:v>
@@ -4414,10 +4420,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
         <x:v>47</x:v>
@@ -4426,10 +4432,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
         <x:v>47</x:v>
@@ -4450,10 +4456,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
         <x:v>47</x:v>
@@ -4462,10 +4468,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
         <x:v>47</x:v>
@@ -4474,13 +4480,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AM31" s="12">
         <x:v>19</x:v>
@@ -4498,10 +4504,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>47</x:v>
@@ -4510,42 +4516,42 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX31" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY31" s="12">
-        <x:v>111</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BA31" s="12">
-        <x:v>156</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:54">
       <x:c r="A32" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>47</x:v>
@@ -4566,10 +4572,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>47</x:v>
@@ -4578,10 +4584,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
         <x:v>47</x:v>
@@ -4590,10 +4596,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
         <x:v>47</x:v>
@@ -4614,10 +4620,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>47</x:v>
@@ -4626,10 +4632,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>47</x:v>
@@ -4638,13 +4644,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="AM32" s="12">
         <x:v>20</x:v>
@@ -4662,10 +4668,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
         <x:v>47</x:v>
@@ -4674,22 +4680,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY32" s="12">
-        <x:v>26</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BA32" s="12">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
         <x:v>109</x:v>
@@ -4700,16 +4706,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
         <x:v>47</x:v>
@@ -4730,10 +4736,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>47</x:v>
@@ -4742,10 +4748,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
         <x:v>47</x:v>
@@ -4754,10 +4760,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
         <x:v>47</x:v>
@@ -4778,10 +4784,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>47</x:v>
@@ -4790,10 +4796,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>47</x:v>
@@ -4802,10 +4808,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>47</x:v>
@@ -4826,10 +4832,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
         <x:v>47</x:v>
@@ -4838,42 +4844,42 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY33" s="12">
-        <x:v>52</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BA33" s="12">
-        <x:v>136</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:54">
       <x:c r="A34" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>47</x:v>
@@ -4894,10 +4900,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>47</x:v>
@@ -4909,7 +4915,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
         <x:v>47</x:v>
@@ -4921,7 +4927,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
         <x:v>47</x:v>
@@ -4942,10 +4948,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>47</x:v>
@@ -4954,10 +4960,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>47</x:v>
@@ -4966,13 +4972,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AM34" s="12">
         <x:v>22</x:v>
@@ -4990,10 +4996,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>47</x:v>
@@ -5002,42 +5008,42 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY34" s="12">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BA34" s="12">
-        <x:v>81</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:54">
       <x:c r="A35" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>47</x:v>
@@ -5058,10 +5064,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
         <x:v>47</x:v>
@@ -5070,10 +5076,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
         <x:v>47</x:v>
@@ -5082,10 +5088,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="U35" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="U35" s="12" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
         <x:v>47</x:v>
@@ -5106,10 +5112,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>47</x:v>
@@ -5118,10 +5124,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AF35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>47</x:v>
@@ -5130,13 +5136,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM35" s="12">
         <x:v>23</x:v>
@@ -5154,10 +5160,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
         <x:v>47</x:v>
@@ -5166,42 +5172,42 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY35" s="12">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AZ35" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BA35" s="12">
-        <x:v>82</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:54">
       <x:c r="A36" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>47</x:v>
@@ -5222,10 +5228,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
         <x:v>47</x:v>
@@ -5234,10 +5240,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
         <x:v>47</x:v>
@@ -5246,10 +5252,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
         <x:v>47</x:v>
@@ -5270,10 +5276,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>47</x:v>
@@ -5282,10 +5288,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>47</x:v>
@@ -5294,13 +5300,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AM36" s="12">
         <x:v>24</x:v>
@@ -5318,10 +5324,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>47</x:v>
@@ -5330,42 +5336,42 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY36" s="12">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="AZ36" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BA36" s="12">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:54">
       <x:c r="A37" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>47</x:v>
@@ -5386,10 +5392,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>47</x:v>
@@ -5398,10 +5404,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
         <x:v>47</x:v>
@@ -5410,10 +5416,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>47</x:v>
@@ -5434,10 +5440,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>47</x:v>
@@ -5446,10 +5452,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>47</x:v>
@@ -5458,13 +5464,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AM37" s="12">
         <x:v>25</x:v>
@@ -5482,10 +5488,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>47</x:v>
@@ -5494,33 +5500,33 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY37" s="12">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BA37" s="12">
-        <x:v>100</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:54">
       <x:c r="A38" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
@@ -5529,7 +5535,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>47</x:v>
@@ -5550,10 +5556,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>47</x:v>
@@ -5562,7 +5568,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
         <x:v>47</x:v>
@@ -5574,7 +5580,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
         <x:v>47</x:v>
@@ -5598,7 +5604,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>47</x:v>
@@ -5610,10 +5616,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>47</x:v>
@@ -5622,13 +5628,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AM38" s="12">
         <x:v>26</x:v>
@@ -5646,10 +5652,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>47</x:v>
@@ -5658,10 +5664,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
         <x:v>47</x:v>
@@ -5670,30 +5676,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AZ38" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BA38" s="12">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:54">
       <x:c r="A39" s="11" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>47</x:v>
@@ -5714,10 +5720,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>47</x:v>
@@ -5726,10 +5732,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
         <x:v>47</x:v>
@@ -5738,10 +5744,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
         <x:v>47</x:v>
@@ -5762,10 +5768,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>47</x:v>
@@ -5774,10 +5780,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>47</x:v>
@@ -5786,10 +5792,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>47</x:v>
@@ -5810,10 +5816,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>47</x:v>
@@ -5822,42 +5828,42 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY39" s="12">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA39" s="12">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:54">
       <x:c r="A40" s="11" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>47</x:v>
@@ -5878,10 +5884,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>47</x:v>
@@ -5890,10 +5896,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
         <x:v>47</x:v>
@@ -5902,10 +5908,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>47</x:v>
@@ -5926,10 +5932,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>47</x:v>
@@ -5938,10 +5944,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>47</x:v>
@@ -5950,13 +5956,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM40" s="12">
         <x:v>28</x:v>
@@ -5974,10 +5980,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>47</x:v>
@@ -5986,42 +5992,42 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY40" s="12">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AZ40" s="12" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="BA40" s="12">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="BB40" s="12" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="AZ40" s="12" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="BA40" s="12">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="BB40" s="12" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:54">
       <x:c r="A41" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>47</x:v>
@@ -6042,7 +6048,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
         <x:v>67</x:v>
@@ -6054,10 +6060,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
         <x:v>47</x:v>
@@ -6066,10 +6072,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
         <x:v>47</x:v>
@@ -6090,10 +6096,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>47</x:v>
@@ -6102,10 +6108,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>47</x:v>
@@ -6114,10 +6120,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>47</x:v>
@@ -6138,10 +6144,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>47</x:v>
@@ -6150,33 +6156,33 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY41" s="12">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AZ41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BA41" s="12">
-        <x:v>85</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:54">
       <x:c r="A42" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
@@ -6185,7 +6191,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>47</x:v>
@@ -6209,7 +6215,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>47</x:v>
@@ -6221,7 +6227,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
         <x:v>47</x:v>
@@ -6233,7 +6239,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>47</x:v>
@@ -6257,7 +6263,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>47</x:v>
@@ -6269,7 +6275,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>47</x:v>
@@ -6281,7 +6287,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>47</x:v>
@@ -6305,7 +6311,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>47</x:v>
@@ -6317,39 +6323,39 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY42" s="12">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA42" s="12">
-        <x:v>125</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:54">
       <x:c r="A43" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
         <x:v>47</x:v>
@@ -6370,10 +6376,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>47</x:v>
@@ -6382,10 +6388,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
         <x:v>47</x:v>
@@ -6394,10 +6400,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>47</x:v>
@@ -6418,10 +6424,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>47</x:v>
@@ -6430,10 +6436,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>47</x:v>
@@ -6445,10 +6451,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AM43" s="12">
         <x:v>31</x:v>
@@ -6466,10 +6472,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
         <x:v>47</x:v>
@@ -6478,42 +6484,42 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY43" s="12">
-        <x:v>0</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="BA43" s="12">
-        <x:v>6</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:54">
       <x:c r="A44" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
         <x:v>47</x:v>
@@ -6534,10 +6540,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>47</x:v>
@@ -6549,7 +6555,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
         <x:v>47</x:v>
@@ -6558,10 +6564,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
         <x:v>47</x:v>
@@ -6582,10 +6588,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>47</x:v>
@@ -6594,10 +6600,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>47</x:v>
@@ -6606,10 +6612,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
         <x:v>47</x:v>
@@ -6630,10 +6636,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>47</x:v>
@@ -6642,42 +6648,42 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY44" s="12">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BA44" s="12">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:54">
       <x:c r="A45" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
         <x:v>47</x:v>
@@ -6698,10 +6704,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>47</x:v>
@@ -6710,10 +6716,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
         <x:v>47</x:v>
@@ -6722,10 +6728,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
         <x:v>47</x:v>
@@ -6746,10 +6752,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>47</x:v>
@@ -6758,10 +6764,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
         <x:v>47</x:v>
@@ -6770,10 +6776,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>47</x:v>
@@ -6794,7 +6800,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
         <x:v>67</x:v>
@@ -6806,42 +6812,42 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY45" s="12">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BA45" s="12">
-        <x:v>66</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:54">
       <x:c r="A46" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>47</x:v>
@@ -6862,10 +6868,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>47</x:v>
@@ -6874,10 +6880,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
         <x:v>47</x:v>
@@ -6886,10 +6892,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
         <x:v>47</x:v>
@@ -6910,10 +6916,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>47</x:v>
@@ -6922,10 +6928,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>47</x:v>
@@ -6934,7 +6940,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
         <x:v>47</x:v>
@@ -6958,10 +6964,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
         <x:v>47</x:v>
@@ -6970,42 +6976,42 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY46" s="12">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA46" s="12">
-        <x:v>70</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:54">
       <x:c r="A47" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>47</x:v>
@@ -7026,10 +7032,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>47</x:v>
@@ -7038,10 +7044,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
         <x:v>47</x:v>
@@ -7050,10 +7056,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
         <x:v>47</x:v>
@@ -7074,10 +7080,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>47</x:v>
@@ -7089,7 +7095,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>47</x:v>
@@ -7098,10 +7104,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>47</x:v>
@@ -7122,10 +7128,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>47</x:v>
@@ -7134,22 +7140,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY47" s="12">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA47" s="12">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
@@ -7157,19 +7163,19 @@
     </x:row>
     <x:row r="48" spans="1:54">
       <x:c r="A48" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>47</x:v>
@@ -7193,7 +7199,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>47</x:v>
@@ -7202,10 +7208,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
         <x:v>47</x:v>
@@ -7214,10 +7220,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
         <x:v>47</x:v>
@@ -7238,10 +7244,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>47</x:v>
@@ -7250,10 +7256,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>47</x:v>
@@ -7262,13 +7268,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM48" s="12">
         <x:v>36</x:v>
@@ -7286,10 +7292,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>47</x:v>
@@ -7298,39 +7304,39 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY48" s="12">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BA48" s="12">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:54">
       <x:c r="A49" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
         <x:v>67</x:v>
@@ -7354,10 +7360,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>47</x:v>
@@ -7366,10 +7372,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
         <x:v>47</x:v>
@@ -7378,10 +7384,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>47</x:v>
@@ -7402,10 +7408,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>47</x:v>
@@ -7414,10 +7420,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>47</x:v>
@@ -7426,10 +7432,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>47</x:v>
@@ -7450,10 +7456,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>47</x:v>
@@ -7462,42 +7468,42 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY49" s="12">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA49" s="12">
-        <x:v>84</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:54">
       <x:c r="A50" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>47</x:v>
@@ -7521,7 +7527,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>47</x:v>
@@ -7533,7 +7539,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
         <x:v>47</x:v>
@@ -7542,10 +7548,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
         <x:v>47</x:v>
@@ -7566,10 +7572,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD50" s="12" t="s">
         <x:v>47</x:v>
@@ -7581,7 +7587,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>47</x:v>
@@ -7590,13 +7596,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM50" s="12">
         <x:v>38</x:v>
@@ -7614,10 +7620,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>47</x:v>
@@ -7626,42 +7632,42 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY50" s="12">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="BA50" s="12">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:54">
       <x:c r="A51" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>47</x:v>
@@ -7682,10 +7688,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>47</x:v>
@@ -7694,10 +7700,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
         <x:v>47</x:v>
@@ -7706,10 +7712,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
         <x:v>47</x:v>
@@ -7730,10 +7736,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>47</x:v>
@@ -7742,10 +7748,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>47</x:v>
@@ -7754,10 +7760,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>47</x:v>
@@ -7778,10 +7784,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>47</x:v>
@@ -7793,36 +7799,36 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY51" s="12">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BA51" s="12">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:54">
       <x:c r="A52" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
         <x:v>47</x:v>
@@ -7846,10 +7852,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>47</x:v>
@@ -7858,10 +7864,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R52" s="12" t="s">
         <x:v>47</x:v>
@@ -7870,7 +7876,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
         <x:v>47</x:v>
@@ -7894,10 +7900,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>47</x:v>
@@ -7906,10 +7912,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>47</x:v>
@@ -7918,13 +7924,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AM52" s="12">
         <x:v>40</x:v>
@@ -7942,10 +7948,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
         <x:v>47</x:v>
@@ -7954,42 +7960,42 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX52" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY52" s="12">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA52" s="12">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:54">
       <x:c r="A53" s="11" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>47</x:v>
@@ -8013,7 +8019,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N53" s="12" t="s">
         <x:v>47</x:v>
@@ -8022,10 +8028,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
         <x:v>47</x:v>
@@ -8034,10 +8040,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
         <x:v>47</x:v>
@@ -8058,10 +8064,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>47</x:v>
@@ -8070,10 +8076,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>47</x:v>
@@ -8082,13 +8088,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM53" s="12">
         <x:v>41</x:v>
@@ -8106,10 +8112,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>47</x:v>
@@ -8118,42 +8124,42 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY53" s="12">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BA53" s="12">
-        <x:v>17</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:54">
       <x:c r="A54" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>47</x:v>
@@ -8174,10 +8180,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>47</x:v>
@@ -8186,10 +8192,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
         <x:v>47</x:v>
@@ -8198,10 +8204,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>47</x:v>
@@ -8222,10 +8228,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>47</x:v>
@@ -8234,10 +8240,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>47</x:v>
@@ -8246,13 +8252,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AM54" s="12">
         <x:v>42</x:v>
@@ -8270,10 +8276,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>47</x:v>
@@ -8282,42 +8288,42 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY54" s="12">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="BA54" s="12">
-        <x:v>76</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:54">
       <x:c r="A55" s="11" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>47</x:v>
@@ -8338,10 +8344,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>47</x:v>
@@ -8350,10 +8356,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R55" s="12" t="s">
         <x:v>47</x:v>
@@ -8362,10 +8368,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>47</x:v>
@@ -8386,10 +8392,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>47</x:v>
@@ -8398,10 +8404,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>47</x:v>
@@ -8410,13 +8416,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM55" s="12">
         <x:v>43</x:v>
@@ -8434,10 +8440,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
         <x:v>47</x:v>
@@ -8446,39 +8452,39 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX55" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY55" s="12">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="BA55" s="12">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:54">
       <x:c r="A56" s="11" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
         <x:v>47</x:v>
@@ -8502,10 +8508,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>47</x:v>
@@ -8514,7 +8520,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
         <x:v>47</x:v>
@@ -8526,7 +8532,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
         <x:v>47</x:v>
@@ -8550,7 +8556,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
         <x:v>47</x:v>
@@ -8562,7 +8568,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
         <x:v>47</x:v>
@@ -8574,7 +8580,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
         <x:v>47</x:v>
@@ -8598,10 +8604,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>47</x:v>
@@ -8610,33 +8616,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY56" s="12">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BA56" s="12">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:54">
       <x:c r="A57" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C57" s="12">
         <x:v>45</x:v>
@@ -8666,10 +8672,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>47</x:v>
@@ -8678,7 +8684,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
         <x:v>47</x:v>
@@ -8690,7 +8696,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
         <x:v>47</x:v>
@@ -8714,10 +8720,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>47</x:v>
@@ -8726,10 +8732,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>47</x:v>
@@ -8738,13 +8744,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AK57" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AL57" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="AK57" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AL57" s="12" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="AM57" s="12">
         <x:v>45</x:v>
@@ -8762,10 +8768,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>47</x:v>
@@ -8774,203 +8780,203 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY57" s="12">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="BA57" s="12">
-        <x:v>92</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:54">
       <x:c r="A58" s="11" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D58" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E58" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L58" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M58" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="N58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="P58" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="Q58" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="R58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="T58" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U58" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="V58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="W58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="X58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Y58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Z58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AA58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AB58" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="AC58" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AD58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AE58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AF58" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AG58" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D58" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E58" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L58" s="12" t="s">
+      <x:c r="AH58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AI58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AJ58" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AK58" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AL58" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AM58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AN58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AO58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AP58" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AQ58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AR58" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="AS58" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="M58" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="P58" s="12" t="s">
+      <x:c r="AT58" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AU58" s="12">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AV58" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AW58" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="Q58" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="R58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="S58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="T58" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U58" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="V58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="W58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="X58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Y58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Z58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AA58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AB58" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AC58" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AD58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AE58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AF58" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AG58" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AH58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AI58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AJ58" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AK58" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AL58" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AM58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AN58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AO58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AP58" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AQ58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AR58" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="AS58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AT58" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AU58" s="12">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AV58" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="AW58" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="AX58" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY58" s="12">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="BA58" s="12">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="BB58" s="12" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="BA58" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="BB58" s="12" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:54">
       <x:c r="A59" s="11" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
         <x:v>47</x:v>
@@ -8994,7 +9000,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
         <x:v>53</x:v>
@@ -9006,10 +9012,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="P59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
         <x:v>47</x:v>
@@ -9018,7 +9024,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
         <x:v>47</x:v>
@@ -9042,10 +9048,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>47</x:v>
@@ -9054,10 +9060,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>47</x:v>
@@ -9066,13 +9072,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AM59" s="12">
         <x:v>47</x:v>
@@ -9093,7 +9099,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>47</x:v>
@@ -9102,42 +9108,42 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY59" s="12">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BA59" s="12">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:54">
       <x:c r="A60" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F60" s="12" t="s">
         <x:v>47</x:v>
@@ -9158,10 +9164,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="L60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M60" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N60" s="12" t="s">
         <x:v>47</x:v>
@@ -9170,10 +9176,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="P60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q60" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R60" s="12" t="s">
         <x:v>47</x:v>
@@ -9182,10 +9188,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="T60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V60" s="12" t="s">
         <x:v>47</x:v>
@@ -9206,10 +9212,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AB60" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
         <x:v>47</x:v>
@@ -9218,10 +9224,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AF60" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH60" s="12" t="s">
         <x:v>47</x:v>
@@ -9230,10 +9236,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
         <x:v>47</x:v>
@@ -9254,7 +9260,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AR60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
         <x:v>47</x:v>
@@ -9266,42 +9272,42 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AV60" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX60" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY60" s="12">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ60" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA60" s="12">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:54">
       <x:c r="A61" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
         <x:v>47</x:v>
@@ -9322,10 +9328,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M61" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N61" s="12" t="s">
         <x:v>47</x:v>
@@ -9334,10 +9340,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="P61" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="R61" s="12" t="s">
         <x:v>47</x:v>
@@ -9346,10 +9352,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="T61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V61" s="12" t="s">
         <x:v>47</x:v>
@@ -9370,10 +9376,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AB61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="s">
         <x:v>47</x:v>
@@ -9382,7 +9388,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
         <x:v>59</x:v>
@@ -9394,13 +9400,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AJ61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM61" s="12">
         <x:v>49</x:v>
@@ -9418,10 +9424,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AR61" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AS61" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="AS61" s="12" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>47</x:v>
@@ -9430,42 +9436,42 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX61" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY61" s="12">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BA61" s="12">
-        <x:v>117</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:54">
       <x:c r="A62" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
         <x:v>47</x:v>
@@ -9486,10 +9492,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
         <x:v>47</x:v>
@@ -9498,10 +9504,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="P62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R62" s="12" t="s">
         <x:v>47</x:v>
@@ -9510,10 +9516,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
         <x:v>47</x:v>
@@ -9534,10 +9540,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
         <x:v>47</x:v>
@@ -9546,10 +9552,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
         <x:v>47</x:v>
@@ -9558,13 +9564,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AM62" s="12">
         <x:v>50</x:v>
@@ -9582,10 +9588,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
         <x:v>47</x:v>
@@ -9594,42 +9600,42 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY62" s="12">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA62" s="12">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:54">
       <x:c r="A63" s="11" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D63" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E63" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F63" s="12" t="s">
         <x:v>47</x:v>
@@ -9665,7 +9671,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Q63" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R63" s="12" t="s">
         <x:v>47</x:v>
@@ -9674,10 +9680,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="T63" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U63" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V63" s="12" t="s">
         <x:v>47</x:v>
@@ -9698,10 +9704,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AB63" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC63" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD63" s="12" t="s">
         <x:v>47</x:v>
@@ -9710,10 +9716,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AF63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG63" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH63" s="12" t="s">
         <x:v>47</x:v>
@@ -9722,13 +9728,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AJ63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK63" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL63" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AM63" s="12">
         <x:v>51</x:v>
@@ -9746,10 +9752,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AR63" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AS63" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="AS63" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="AT63" s="12" t="s">
         <x:v>47</x:v>
@@ -9758,206 +9764,206 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AV63" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW63" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX63" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY63" s="12">
-        <x:v>92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AZ63" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BA63" s="12">
-        <x:v>78</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:54">
       <x:c r="A64" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C64" s="12">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L64" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M64" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="P64" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q64" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="R64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="T64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="U64" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="V64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="W64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="X64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Y64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Z64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AA64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AB64" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AC64" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AD64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AE64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AF64" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AH64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AI64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AJ64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AK64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AL64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AM64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AN64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AO64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AP64" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AQ64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AR64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AS64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AT64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AU64" s="12">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AV64" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AW64" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AX64" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AY64" s="12">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="AZ64" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="L64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M64" s="12" t="s">
+      <x:c r="BA64" s="12">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="N64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Q64" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="R64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="S64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="T64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="U64" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="V64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="W64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="X64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Y64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="Z64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AA64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AB64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AC64" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AD64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AE64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AF64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AG64" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AH64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AI64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AJ64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AK64" s="12" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AL64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AM64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AN64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AO64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AP64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AQ64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AR64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AS64" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AT64" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AU64" s="12">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AV64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AW64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AX64" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="AY64" s="12">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AZ64" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BA64" s="12">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="BB64" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:54">
       <x:c r="A65" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F65" s="12" t="s">
         <x:v>47</x:v>
@@ -9978,10 +9984,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="L65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N65" s="12" t="s">
         <x:v>47</x:v>
@@ -9990,10 +9996,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
         <x:v>47</x:v>
@@ -10002,10 +10008,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="T65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V65" s="12" t="s">
         <x:v>47</x:v>
@@ -10026,10 +10032,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
         <x:v>47</x:v>
@@ -10038,10 +10044,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
         <x:v>47</x:v>
@@ -10050,13 +10056,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL65" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AM65" s="12">
         <x:v>53</x:v>
@@ -10074,10 +10080,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT65" s="12" t="s">
         <x:v>47</x:v>
@@ -10086,102 +10092,102 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX65" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AY65" s="12">
-        <x:v>35</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="BA65" s="12">
-        <x:v>35</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:54">
       <x:c r="A66" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B66" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C66" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D66" s="7"/>
       <x:c r="E66" s="7"/>
       <x:c r="F66" s="7"/>
       <x:c r="G66" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H66" s="7"/>
       <x:c r="I66" s="7"/>
       <x:c r="J66" s="7"/>
       <x:c r="K66" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="L66" s="7"/>
       <x:c r="M66" s="7"/>
       <x:c r="N66" s="7"/>
       <x:c r="O66" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="P66" s="7"/>
       <x:c r="Q66" s="7"/>
       <x:c r="R66" s="7"/>
       <x:c r="S66" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="T66" s="7"/>
       <x:c r="U66" s="7"/>
       <x:c r="V66" s="7"/>
       <x:c r="W66" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="X66" s="7"/>
       <x:c r="Y66" s="7"/>
       <x:c r="Z66" s="7"/>
       <x:c r="AA66" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="AB66" s="7"/>
       <x:c r="AC66" s="7"/>
       <x:c r="AD66" s="7"/>
       <x:c r="AE66" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="AF66" s="7"/>
       <x:c r="AG66" s="7"/>
       <x:c r="AH66" s="7"/>
       <x:c r="AI66" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="AJ66" s="7"/>
       <x:c r="AK66" s="7"/>
       <x:c r="AL66" s="7"/>
       <x:c r="AM66" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="AN66" s="7"/>
       <x:c r="AO66" s="7"/>
       <x:c r="AP66" s="7"/>
       <x:c r="AQ66" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="AR66" s="7"/>
       <x:c r="AS66" s="7"/>
       <x:c r="AT66" s="7"/>
       <x:c r="AU66" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="AV66" s="7"/>
       <x:c r="AW66" s="7"/>
@@ -10193,37 +10199,37 @@
     </x:row>
     <x:row r="68" spans="1:54">
       <x:c r="A68" s="14" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:54">
       <x:c r="A69" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:54">
       <x:c r="A70" s="13" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:54">
       <x:c r="A71" s="13" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:54">
       <x:c r="A72" s="13" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:54">
       <x:c r="A73" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:54">
       <x:c r="A74" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
